--- a/data/trans_orig/IP19D-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19D-Edad-trans_orig.xlsx
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>63,1%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36524</t>
+          <t>37055</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51357</t>
+          <t>51647</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34481</t>
+          <t>34336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48003</t>
+          <t>48297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75244</t>
+          <t>76344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95950</t>
+          <t>96835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,72%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>9394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28928</t>
+          <t>28028</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43080</t>
+          <t>42611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27418</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40829</t>
+          <t>41437</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>59772</t>
+          <t>58768</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>80860</t>
+          <t>80043</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47264</t>
+          <t>47812</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>62970</t>
+          <t>63603</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51359</t>
+          <t>51151</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68296</t>
+          <t>68487</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>103707</t>
+          <t>103684</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>126114</t>
+          <t>125883</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,31%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>5895</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11386</t>
+          <t>11744</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>28144</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44048</t>
+          <t>43716</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34832</t>
+          <t>35171</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51837</t>
+          <t>51812</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68551</t>
+          <t>69186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>91027</t>
+          <t>91316</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>108926</t>
+          <t>109388</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127551</t>
+          <t>128365</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114462</t>
+          <t>114684</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>132832</t>
+          <t>133258</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>230314</t>
+          <t>230251</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>257506</t>
+          <t>254956</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,65%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>532</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30028</t>
+          <t>29817</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47436</t>
+          <t>47777</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>30147</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47647</t>
+          <t>47476</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63314</t>
+          <t>64106</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87624</t>
+          <t>88330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9932</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>206710</t>
+          <t>207600</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>237423</t>
+          <t>237500</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>212105</t>
+          <t>211900</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>241785</t>
+          <t>241549</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>427332</t>
+          <t>427426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>466782</t>
+          <t>469310</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>25392</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>95956</t>
+          <t>95731</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>125367</t>
+          <t>124167</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>101795</t>
+          <t>101640</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>130563</t>
+          <t>130696</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>207701</t>
+          <t>207297</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>247002</t>
+          <t>248226</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,47%</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29269</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44086</t>
+          <t>43680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26509</t>
+          <t>26794</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42716</t>
+          <t>42834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59330</t>
+          <t>58907</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82241</t>
+          <t>81604</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,13%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30829</t>
+          <t>30920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45131</t>
+          <t>45340</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42862</t>
+          <t>41515</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59743</t>
+          <t>58854</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77902</t>
+          <t>78158</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>99887</t>
+          <t>101416</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45494</t>
+          <t>44110</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64038</t>
+          <t>63276</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45825</t>
+          <t>45984</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63849</t>
+          <t>64476</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>97279</t>
+          <t>95956</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>122023</t>
+          <t>121034</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12810</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16725</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59819</t>
+          <t>59571</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78075</t>
+          <t>78289</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57855</t>
+          <t>57624</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76177</t>
+          <t>76118</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123154</t>
+          <t>123216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>148365</t>
+          <t>149968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,2%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12487</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71807</t>
+          <t>72029</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91389</t>
+          <t>91240</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72517</t>
+          <t>73115</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91728</t>
+          <t>92302</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>151419</t>
+          <t>151379</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>178590</t>
+          <t>178531</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>660</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49230</t>
+          <t>48400</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68081</t>
+          <t>68348</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42063</t>
+          <t>42082</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60416</t>
+          <t>60783</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96292</t>
+          <t>95772</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122570</t>
+          <t>123133</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>157786</t>
+          <t>157991</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>189593</t>
+          <t>187322</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>156224</t>
+          <t>156736</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>189022</t>
+          <t>190107</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>323262</t>
+          <t>324611</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>367097</t>
+          <t>368551</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>23372</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32528</t>
+          <t>32385</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>150768</t>
+          <t>152541</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>183591</t>
+          <t>182451</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>152713</t>
+          <t>152466</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>184650</t>
+          <t>185693</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>315884</t>
+          <t>314041</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>359062</t>
+          <t>357370</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,67%</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23712</t>
+          <t>23492</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37046</t>
+          <t>36451</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33864</t>
+          <t>33807</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48253</t>
+          <t>48176</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60371</t>
+          <t>61671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80292</t>
+          <t>80903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,35%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24443</t>
+          <t>25312</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37616</t>
+          <t>38052</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25696</t>
+          <t>25753</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40096</t>
+          <t>39625</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>54533</t>
+          <t>53981</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74458</t>
+          <t>73526</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73943</t>
+          <t>74169</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94110</t>
+          <t>93505</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62767</t>
+          <t>62956</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83026</t>
+          <t>84281</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>143560</t>
+          <t>142150</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>172728</t>
+          <t>170710</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15034</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>17657</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42595</t>
+          <t>43750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61477</t>
+          <t>61756</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59407</t>
+          <t>58650</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79347</t>
+          <t>79745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107750</t>
+          <t>108252</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>135447</t>
+          <t>136343</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,24%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86274</t>
+          <t>86496</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105159</t>
+          <t>105248</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82072</t>
+          <t>82316</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100421</t>
+          <t>100679</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>175276</t>
+          <t>175714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>201343</t>
+          <t>200647</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>331</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32927</t>
+          <t>32661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>51297</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>30967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49161</t>
+          <t>49254</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68071</t>
+          <t>68444</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93926</t>
+          <t>93353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>12915</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22206</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>195975</t>
+          <t>194832</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>225812</t>
+          <t>225331</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>190170</t>
+          <t>190288</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>221690</t>
+          <t>222124</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>392829</t>
+          <t>395099</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>437516</t>
+          <t>437752</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,58%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23845</t>
+          <t>23903</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16426</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30641</t>
+          <t>31964</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>109721</t>
+          <t>111049</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>139371</t>
+          <t>141241</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>128649</t>
+          <t>127986</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>159801</t>
+          <t>159245</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>247456</t>
+          <t>246997</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>290473</t>
+          <t>288664</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>307</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>41,86%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46641</t>
+          <t>46730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57213</t>
+          <t>58035</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49167</t>
+          <t>48087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63731</t>
+          <t>62959</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100882</t>
+          <t>100750</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118442</t>
+          <t>117864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>798</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25727</t>
+          <t>26441</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21726</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38537</t>
+          <t>38898</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80162</t>
+          <t>80564</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>99199</t>
+          <t>99212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>117404</t>
+          <t>117498</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>137621</t>
+          <t>137623</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>205570</t>
+          <t>203707</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>230666</t>
+          <t>232533</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>20102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38389</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26335</t>
+          <t>26099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46978</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51974</t>
+          <t>50796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77449</t>
+          <t>78899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>319</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154332</t>
+          <t>155762</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>171869</t>
+          <t>172699</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>180078</t>
+          <t>180205</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205704</t>
+          <t>205817</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>341012</t>
+          <t>340894</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>373049</t>
+          <t>373072</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8425</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24349</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41198</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27463</t>
+          <t>27112</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52930</t>
+          <t>52463</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56048</t>
+          <t>55965</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88129</t>
+          <t>87902</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,39 +12255,39 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5060</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>4561</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>297619</t>
+          <t>297664</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>325163</t>
+          <t>325569</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>363788</t>
+          <t>363011</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>400066</t>
+          <t>401364</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>675377</t>
+          <t>675793</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>719595</t>
+          <t>719494</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12510</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60598</t>
+          <t>60905</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>88174</t>
+          <t>88060</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>77251</t>
+          <t>75990</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>112774</t>
+          <t>111955</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>143848</t>
+          <t>142608</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>187968</t>
+          <t>186106</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
